--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-04.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,37 +634,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EUROPA CHAMPIONS LEAGUE</t>
+          <t>BULGARIA 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ararat Armenia x NK Celje</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ararat Armenia</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NK Celje</t>
-        </is>
-      </c>
+          <t>Montana x Nesebar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -661,37 +665,45 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="L3" t="n">
-        <v>6.25</v>
+        <v>7.14</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,7 +713,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -711,27 +723,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb x FK Kauno Zalgiris</t>
+          <t>Ararat Armenia x NK Celje</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Ararat Armenia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -740,20 +752,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11.36</v>
+        <v>6.25</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -771,6 +783,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,37 +794,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>EUROPA CHAMPIONS LEAGUE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Larne x FC Iberia 1999</t>
+          <t>Dinamo Zagreb x FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -819,20 +833,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="L5" t="n">
-        <v>3.03</v>
+        <v>11.36</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,6 +864,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -869,27 +885,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers x Egnatia Rrogozhine</t>
+          <t>Larne x FC Iberia 1999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +914,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5.88</v>
+        <v>3.03</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +945,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,37 +956,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Carabobo FC x Trujillanos</t>
+          <t>Shamrock Rovers x Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,20 +995,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="K7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.81</v>
+        <v>5.88</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1008,6 +1026,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1027,19 +1047,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Carabobo x Trujillanos</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>Carabobo FC x Trujillanos</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trujillanos</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1048,13 +1076,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
         <v>1.39</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699999999999999</v>
+        <v>23.81</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -1066,25 +1094,21 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="T8" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1094,17 +1118,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BULGARIA 2</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Montana x Nesebar</t>
+          <t>Carabobo x Trujillanos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1125,20 +1149,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="L9" t="n">
-        <v>7.14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1152,15 +1176,106 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="T9" t="b">
+        <v>8.4</v>
+      </c>
+      <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deportes Tolima x Ind. Medellin</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ind. Medellin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>26</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>200</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7.72</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-04.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-04.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
